--- a/skills/분개테스트/examples/모의자료/분개장_2026_기말후.xlsx
+++ b/skills/분개테스트/examples/모의자료/분개장_2026_기말후.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -51,11 +53,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I303"/>
+  <dimension ref="A1:L303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -433,6 +436,9 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,6 +487,21 @@
           <t>거래처</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>작성자</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>승인자</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>입력일시</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -520,6 +541,19 @@
           <t>대한소재</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>46031.38194444445</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -559,6 +593,19 @@
           <t>대한소재</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>46031.38194444445</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -598,6 +645,19 @@
           <t>대한소재</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>46031.38194444445</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -637,6 +697,19 @@
           <t>정우금속</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>46031.40763888889</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -676,6 +749,19 @@
           <t>정우금속</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>46031.40763888889</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -715,6 +801,19 @@
           <t>정우금속</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>46031.40763888889</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -754,6 +853,19 @@
           <t>한성부품</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>46031.43333333333</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -793,6 +905,19 @@
           <t>한성부품</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>46031.43333333333</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -832,6 +957,19 @@
           <t>한성부품</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>46031.43333333333</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -871,6 +1009,19 @@
           <t>동진케미칼</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>46031.45902777778</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -910,6 +1061,19 @@
           <t>동진케미칼</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>46031.45902777778</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -949,6 +1113,19 @@
           <t>동진케미칼</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>46031.45902777778</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -988,6 +1165,19 @@
           <t>서림물산</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>46031.48472222222</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1027,6 +1217,19 @@
           <t>서림물산</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>46031.48472222222</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1066,6 +1269,19 @@
           <t>서림물산</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>46031.48472222222</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1105,6 +1321,19 @@
           <t>늘푸른산업</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>46031.51041666666</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1144,6 +1373,19 @@
           <t>늘푸른산업</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>46031.51041666666</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1183,6 +1425,19 @@
           <t>늘푸른산업</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>46031.51041666666</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1217,6 +1472,19 @@
           <t>2025년 12월 급여 예수금 납부</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>46031.53611111111</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1251,6 +1519,19 @@
           <t>2025년 12월 급여 예수금 납부</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>46031.53611111111</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1290,6 +1571,19 @@
           <t>에이원테크</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>46034.56180555555</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1329,6 +1623,19 @@
           <t>에이원테크</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>46034.56180555555</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1368,6 +1675,19 @@
           <t>비앤씨산업</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>46036.5875</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1407,6 +1727,19 @@
           <t>비앤씨산업</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>46036.5875</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1446,6 +1779,19 @@
           <t>누리전자</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>46037.61319444444</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1485,6 +1831,19 @@
           <t>누리전자</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>46037.61319444444</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1524,6 +1883,19 @@
           <t>누리전자</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>46037.61319444444</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1563,6 +1935,19 @@
           <t>대영정밀</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>46037.63888888889</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1602,6 +1987,19 @@
           <t>대영정밀</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>46037.63888888889</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1641,6 +2039,19 @@
           <t>대영정밀</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>46037.63888888889</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1680,6 +2091,19 @@
           <t>세진산업</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>46037.66458333333</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1719,6 +2143,19 @@
           <t>세진산업</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>46037.66458333333</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1758,6 +2195,19 @@
           <t>세진산업</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>46037.66458333333</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1797,6 +2247,19 @@
           <t>동원테크</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>46037.69027777778</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1836,6 +2299,19 @@
           <t>동원테크</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>46037.69027777778</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1875,6 +2351,19 @@
           <t>동원테크</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>46037.69027777778</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1914,6 +2403,19 @@
           <t>미래기계</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>46037.38263888889</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1953,6 +2455,19 @@
           <t>미래기계</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>46037.38263888889</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1992,6 +2507,19 @@
           <t>미래기계</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>46037.38263888889</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2031,6 +2559,19 @@
           <t>한빛오토</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>46037.40833333333</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2070,6 +2611,19 @@
           <t>한빛오토</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>46037.40833333333</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2109,6 +2663,19 @@
           <t>한빛오토</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>46037.40833333333</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2148,6 +2715,19 @@
           <t>태성금속</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>46037.43402777778</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2187,6 +2767,19 @@
           <t>태성금속</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>46037.43402777778</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2226,6 +2819,19 @@
           <t>태성금속</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>46037.43402777778</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2265,6 +2871,19 @@
           <t>청솔전자</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>46037.45972222222</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2304,6 +2923,19 @@
           <t>청솔전자</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>46037.45972222222</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2343,6 +2975,19 @@
           <t>청솔전자</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>46037.45972222222</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2382,6 +3027,19 @@
           <t>우진기공</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>46037.48541666667</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2421,6 +3079,19 @@
           <t>우진기공</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>46037.48541666667</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2460,6 +3131,19 @@
           <t>우진기공</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>46037.48541666667</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -2499,6 +3183,19 @@
           <t>보람산업</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>46037.51111111111</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2538,6 +3235,19 @@
           <t>보람산업</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>46037.51111111111</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -2577,6 +3287,19 @@
           <t>보람산업</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>46037.51111111111</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2616,6 +3339,19 @@
           <t>다온테크</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>46037.53680555556</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -2655,6 +3391,19 @@
           <t>다온테크</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>46037.53680555556</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -2694,6 +3443,19 @@
           <t>다온테크</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>46037.53680555556</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -2733,6 +3495,19 @@
           <t>해솔정밀</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>46037.5625</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -2772,6 +3547,19 @@
           <t>해솔정밀</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>46037.5625</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -2811,6 +3599,19 @@
           <t>해솔정밀</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>46037.5625</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -2850,6 +3651,19 @@
           <t>새롬전자</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>46037.58819444444</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -2889,6 +3703,19 @@
           <t>새롬전자</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>46037.58819444444</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -2928,6 +3755,19 @@
           <t>새롬전자</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>46037.58819444444</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -2967,6 +3807,19 @@
           <t>은하산업</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>46037.61388888889</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3006,6 +3859,19 @@
           <t>은하산업</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>46037.61388888889</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -3045,6 +3911,19 @@
           <t>은하산업</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>46037.61388888889</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -3084,6 +3963,19 @@
           <t>이든테크</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>46037.63958333333</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -3123,6 +4015,19 @@
           <t>이든테크</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>46037.63958333333</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -3162,6 +4067,19 @@
           <t>이든테크</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>46037.63958333333</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -3201,6 +4119,19 @@
           <t>한결기계</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>46037.66527777778</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -3240,6 +4171,19 @@
           <t>한결기계</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>46037.66527777778</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -3279,6 +4223,19 @@
           <t>한결기계</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>46037.66527777778</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -3318,6 +4275,19 @@
           <t>지온오토</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>46037.69097222222</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -3357,6 +4327,19 @@
           <t>지온오토</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>46037.69097222222</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -3396,6 +4379,19 @@
           <t>지온오토</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>46037.69097222222</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -3435,6 +4431,19 @@
           <t>유성정밀</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>46037.38333333333</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -3474,6 +4483,19 @@
           <t>유성정밀</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>46037.38333333333</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -3513,6 +4535,19 @@
           <t>유성정밀</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>46037.38333333333</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -3552,6 +4587,19 @@
           <t>라온전자</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>46037.40902777778</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -3591,6 +4639,19 @@
           <t>라온전자</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>46037.40902777778</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -3630,6 +4691,19 @@
           <t>라온전자</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>46037.40902777778</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -3669,6 +4743,19 @@
           <t>나래산업</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>46037.43472222222</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -3708,6 +4795,19 @@
           <t>나래산업</t>
         </is>
       </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="n">
+        <v>46037.43472222222</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -3747,6 +4847,19 @@
           <t>나래산업</t>
         </is>
       </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="n">
+        <v>46037.43472222222</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -3786,6 +4899,19 @@
           <t>세움설비</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>46038.46041666667</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -3825,6 +4951,19 @@
           <t>세움설비</t>
         </is>
       </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>46038.46041666667</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -3864,6 +5003,19 @@
           <t>세움설비</t>
         </is>
       </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>46038.46041666667</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -3903,6 +5055,19 @@
           <t>씨엘상사</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="n">
+        <v>46042.48611111111</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -3942,6 +5107,19 @@
           <t>씨엘상사</t>
         </is>
       </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="n">
+        <v>46042.48611111111</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -3981,6 +5159,19 @@
           <t>누리전자</t>
         </is>
       </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="n">
+        <v>46045.51180555556</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -4020,6 +5211,19 @@
           <t>누리전자</t>
         </is>
       </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="n">
+        <v>46045.51180555556</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -4059,6 +5263,19 @@
           <t>대영정밀</t>
         </is>
       </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="n">
+        <v>46045.5375</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -4098,6 +5315,19 @@
           <t>대영정밀</t>
         </is>
       </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="n">
+        <v>46045.5375</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -4137,6 +5367,19 @@
           <t>세진산업</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="n">
+        <v>46045.56319444445</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -4176,6 +5419,19 @@
           <t>세진산업</t>
         </is>
       </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="n">
+        <v>46045.56319444445</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -4215,6 +5471,19 @@
           <t>동원테크</t>
         </is>
       </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="n">
+        <v>46045.58888888889</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -4254,6 +5523,19 @@
           <t>동원테크</t>
         </is>
       </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="n">
+        <v>46045.58888888889</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -4293,6 +5575,19 @@
           <t>미래기계</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="n">
+        <v>46045.61458333334</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -4332,6 +5627,19 @@
           <t>미래기계</t>
         </is>
       </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="n">
+        <v>46045.61458333334</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -4371,6 +5679,19 @@
           <t>한빛오토</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>46045.64027777778</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -4410,6 +5731,19 @@
           <t>한빛오토</t>
         </is>
       </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>46045.64027777778</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -4449,6 +5783,19 @@
           <t>태성금속</t>
         </is>
       </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="n">
+        <v>46045.66597222222</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -4488,6 +5835,19 @@
           <t>태성금속</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="n">
+        <v>46045.66597222222</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -4527,6 +5887,19 @@
           <t>청솔전자</t>
         </is>
       </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="n">
+        <v>46045.69166666667</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -4566,6 +5939,19 @@
           <t>청솔전자</t>
         </is>
       </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="n">
+        <v>46045.69166666667</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -4605,6 +5991,19 @@
           <t>우진기공</t>
         </is>
       </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="n">
+        <v>46045.38402777778</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -4644,6 +6043,19 @@
           <t>우진기공</t>
         </is>
       </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="n">
+        <v>46045.38402777778</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -4683,6 +6095,19 @@
           <t>보람산업</t>
         </is>
       </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="n">
+        <v>46045.40972222222</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -4722,6 +6147,19 @@
           <t>보람산업</t>
         </is>
       </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="n">
+        <v>46045.40972222222</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -4761,6 +6199,19 @@
           <t>다온테크</t>
         </is>
       </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="n">
+        <v>46045.43541666667</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -4800,6 +6251,19 @@
           <t>다온테크</t>
         </is>
       </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="n">
+        <v>46045.43541666667</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -4839,6 +6303,19 @@
           <t>해솔정밀</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="n">
+        <v>46045.46111111111</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -4878,6 +6355,19 @@
           <t>해솔정밀</t>
         </is>
       </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="n">
+        <v>46045.46111111111</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -4917,6 +6407,19 @@
           <t>새롬전자</t>
         </is>
       </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="n">
+        <v>46045.48680555556</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -4956,6 +6459,19 @@
           <t>새롬전자</t>
         </is>
       </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="n">
+        <v>46045.48680555556</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -4995,6 +6511,19 @@
           <t>은하산업</t>
         </is>
       </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="n">
+        <v>46045.5125</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -5034,6 +6563,19 @@
           <t>은하산업</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L118" s="4" t="n">
+        <v>46045.5125</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -5073,6 +6615,19 @@
           <t>이든테크</t>
         </is>
       </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="n">
+        <v>46045.53819444445</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -5112,6 +6667,19 @@
           <t>이든테크</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L120" s="4" t="n">
+        <v>46045.53819444445</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -5151,6 +6719,19 @@
           <t>한결기계</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="n">
+        <v>46045.56388888889</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -5190,6 +6771,19 @@
           <t>한결기계</t>
         </is>
       </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="n">
+        <v>46045.56388888889</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -5229,6 +6823,19 @@
           <t>지온오토</t>
         </is>
       </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="n">
+        <v>46045.58958333333</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -5268,6 +6875,19 @@
           <t>지온오토</t>
         </is>
       </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="n">
+        <v>46045.58958333333</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -5307,6 +6927,19 @@
           <t>유성정밀</t>
         </is>
       </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="n">
+        <v>46045.61527777778</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -5346,6 +6979,19 @@
           <t>유성정밀</t>
         </is>
       </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="n">
+        <v>46045.61527777778</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -5385,6 +7031,19 @@
           <t>라온전자</t>
         </is>
       </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="n">
+        <v>46045.64097222222</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -5424,6 +7083,19 @@
           <t>라온전자</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="n">
+        <v>46045.64097222222</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -5463,6 +7135,19 @@
           <t>나래산업</t>
         </is>
       </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L129" s="4" t="n">
+        <v>46045.66666666666</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -5502,6 +7187,19 @@
           <t>나래산업</t>
         </is>
       </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="n">
+        <v>46045.66666666666</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -5536,6 +7234,19 @@
           <t>1월 급여</t>
         </is>
       </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="n">
+        <v>46045.69236111111</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -5570,6 +7281,19 @@
           <t>1월 급여 예수금</t>
         </is>
       </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="n">
+        <v>46045.69236111111</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -5604,6 +7328,19 @@
           <t>1월 급여 지급</t>
         </is>
       </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L133" s="4" t="n">
+        <v>46045.69236111111</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -5638,6 +7375,19 @@
           <t>퇴직연금 납부(확정기여형)</t>
         </is>
       </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="n">
+        <v>46045.38472222222</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -5672,6 +7422,19 @@
           <t>퇴직연금 납부(확정기여형)</t>
         </is>
       </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L135" s="4" t="n">
+        <v>46045.38472222222</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -5706,6 +7469,19 @@
           <t>2025년 2기 부가세 확정신고 납부</t>
         </is>
       </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="n">
+        <v>46045.41041666667</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -5740,6 +7516,19 @@
           <t>2025년 2기 부가세 확정신고 납부</t>
         </is>
       </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L137" s="4" t="n">
+        <v>46045.41041666667</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -5774,6 +7563,19 @@
           <t>2025년 2기 부가세 확정신고 납부</t>
         </is>
       </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="n">
+        <v>46045.41041666667</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -5813,6 +7615,19 @@
           <t>대한소재</t>
         </is>
       </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="n">
+        <v>46050.43611111111</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -5852,6 +7667,19 @@
           <t>대한소재</t>
         </is>
       </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="n">
+        <v>46050.43611111111</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -5891,6 +7719,19 @@
           <t>정우금속</t>
         </is>
       </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L141" s="4" t="n">
+        <v>46050.46180555555</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -5930,6 +7771,19 @@
           <t>정우금속</t>
         </is>
       </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="n">
+        <v>46050.46180555555</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -5969,6 +7823,19 @@
           <t>한성부품</t>
         </is>
       </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="n">
+        <v>46050.4875</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -6008,6 +7875,19 @@
           <t>한성부품</t>
         </is>
       </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="n">
+        <v>46050.4875</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -6047,6 +7927,19 @@
           <t>동진케미칼</t>
         </is>
       </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="n">
+        <v>46050.51319444444</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -6086,6 +7979,19 @@
           <t>동진케미칼</t>
         </is>
       </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="n">
+        <v>46050.51319444444</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -6125,6 +8031,19 @@
           <t>서림물산</t>
         </is>
       </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L147" s="4" t="n">
+        <v>46050.53888888889</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -6164,6 +8083,19 @@
           <t>서림물산</t>
         </is>
       </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="n">
+        <v>46050.53888888889</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -6203,6 +8135,19 @@
           <t>늘푸른산업</t>
         </is>
       </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="n">
+        <v>46050.56458333333</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -6242,6 +8187,19 @@
           <t>늘푸른산업</t>
         </is>
       </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="n">
+        <v>46050.56458333333</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -6276,6 +8234,19 @@
           <t>매출원가 대체</t>
         </is>
       </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="n">
+        <v>46055.59027777778</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -6310,6 +8281,19 @@
           <t>매출원가 대체</t>
         </is>
       </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="n">
+        <v>46055.59027777778</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -6349,6 +8333,19 @@
           <t>가나은행</t>
         </is>
       </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L153" s="4" t="n">
+        <v>46055.61597222222</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -6388,6 +8385,19 @@
           <t>가나은행</t>
         </is>
       </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="n">
+        <v>46055.61597222222</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -6427,6 +8437,19 @@
           <t>가나은행</t>
         </is>
       </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="n">
+        <v>46055.64166666667</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -6466,6 +8489,19 @@
           <t>가나은행</t>
         </is>
       </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="n">
+        <v>46055.64166666667</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -6500,6 +8536,19 @@
           <t>기계장치 감가상각</t>
         </is>
       </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L157" s="4" t="n">
+        <v>46055.66736111111</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -6534,6 +8583,19 @@
           <t>기계장치 감가상각</t>
         </is>
       </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L158" s="4" t="n">
+        <v>46055.66736111111</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -6573,6 +8635,19 @@
           <t>대한소재</t>
         </is>
       </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L159" s="4" t="n">
+        <v>46063.69305555556</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -6612,6 +8687,19 @@
           <t>대한소재</t>
         </is>
       </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="n">
+        <v>46063.69305555556</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -6651,6 +8739,19 @@
           <t>대한소재</t>
         </is>
       </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L161" s="4" t="n">
+        <v>46063.69305555556</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -6690,6 +8791,19 @@
           <t>정우금속</t>
         </is>
       </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="n">
+        <v>46063.38541666666</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -6729,6 +8843,19 @@
           <t>정우금속</t>
         </is>
       </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="n">
+        <v>46063.38541666666</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -6768,6 +8895,19 @@
           <t>정우금속</t>
         </is>
       </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="n">
+        <v>46063.38541666666</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -6807,6 +8947,19 @@
           <t>한성부품</t>
         </is>
       </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L165" s="4" t="n">
+        <v>46063.41111111111</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -6846,6 +8999,19 @@
           <t>한성부품</t>
         </is>
       </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="n">
+        <v>46063.41111111111</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -6885,6 +9051,19 @@
           <t>한성부품</t>
         </is>
       </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L167" s="4" t="n">
+        <v>46063.41111111111</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -6924,6 +9103,19 @@
           <t>동진케미칼</t>
         </is>
       </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="n">
+        <v>46063.43680555555</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -6963,6 +9155,19 @@
           <t>동진케미칼</t>
         </is>
       </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L169" s="4" t="n">
+        <v>46063.43680555555</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -7002,6 +9207,19 @@
           <t>동진케미칼</t>
         </is>
       </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="n">
+        <v>46063.43680555555</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -7041,6 +9259,19 @@
           <t>서림물산</t>
         </is>
       </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="n">
+        <v>46063.4625</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -7080,6 +9311,19 @@
           <t>서림물산</t>
         </is>
       </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L172" s="4" t="n">
+        <v>46063.4625</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -7119,6 +9363,19 @@
           <t>서림물산</t>
         </is>
       </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L173" s="4" t="n">
+        <v>46063.4625</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -7158,6 +9415,19 @@
           <t>늘푸른산업</t>
         </is>
       </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L174" s="4" t="n">
+        <v>46063.48819444444</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -7197,6 +9467,19 @@
           <t>늘푸른산업</t>
         </is>
       </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L175" s="4" t="n">
+        <v>46063.48819444444</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -7236,6 +9519,19 @@
           <t>늘푸른산업</t>
         </is>
       </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="n">
+        <v>46063.48819444444</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -7270,6 +9566,19 @@
           <t>2026년 1월 급여 예수금 납부</t>
         </is>
       </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L177" s="4" t="n">
+        <v>46063.51388888889</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -7304,6 +9613,19 @@
           <t>2026년 1월 급여 예수금 납부</t>
         </is>
       </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L178" s="4" t="n">
+        <v>46063.51388888889</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -7343,6 +9665,19 @@
           <t>누리전자</t>
         </is>
       </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L179" s="4" t="n">
+        <v>46066.53958333333</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -7382,6 +9717,19 @@
           <t>누리전자</t>
         </is>
       </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L180" s="4" t="n">
+        <v>46066.53958333333</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -7421,6 +9769,19 @@
           <t>누리전자</t>
         </is>
       </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L181" s="4" t="n">
+        <v>46066.53958333333</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -7460,6 +9821,19 @@
           <t>대영정밀</t>
         </is>
       </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L182" s="4" t="n">
+        <v>46066.56527777778</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -7499,6 +9873,19 @@
           <t>대영정밀</t>
         </is>
       </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L183" s="4" t="n">
+        <v>46066.56527777778</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -7538,6 +9925,19 @@
           <t>대영정밀</t>
         </is>
       </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L184" s="4" t="n">
+        <v>46066.56527777778</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -7577,6 +9977,19 @@
           <t>세진산업</t>
         </is>
       </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L185" s="4" t="n">
+        <v>46066.59097222222</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -7616,6 +10029,19 @@
           <t>세진산업</t>
         </is>
       </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L186" s="4" t="n">
+        <v>46066.59097222222</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -7655,6 +10081,19 @@
           <t>세진산업</t>
         </is>
       </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L187" s="4" t="n">
+        <v>46066.59097222222</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -7694,6 +10133,19 @@
           <t>동원테크</t>
         </is>
       </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L188" s="4" t="n">
+        <v>46066.61666666667</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -7733,6 +10185,19 @@
           <t>동원테크</t>
         </is>
       </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L189" s="4" t="n">
+        <v>46066.61666666667</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -7772,6 +10237,19 @@
           <t>동원테크</t>
         </is>
       </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L190" s="4" t="n">
+        <v>46066.61666666667</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -7811,6 +10289,19 @@
           <t>미래기계</t>
         </is>
       </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L191" s="4" t="n">
+        <v>46066.64236111111</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -7850,6 +10341,19 @@
           <t>미래기계</t>
         </is>
       </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L192" s="4" t="n">
+        <v>46066.64236111111</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -7889,6 +10393,19 @@
           <t>미래기계</t>
         </is>
       </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L193" s="4" t="n">
+        <v>46066.64236111111</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -7928,6 +10445,19 @@
           <t>한빛오토</t>
         </is>
       </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L194" s="4" t="n">
+        <v>46066.66805555556</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -7967,6 +10497,19 @@
           <t>한빛오토</t>
         </is>
       </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L195" s="4" t="n">
+        <v>46066.66805555556</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -8006,6 +10549,19 @@
           <t>한빛오토</t>
         </is>
       </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L196" s="4" t="n">
+        <v>46066.66805555556</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -8045,6 +10601,19 @@
           <t>태성금속</t>
         </is>
       </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L197" s="4" t="n">
+        <v>46066.69375</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -8084,6 +10653,19 @@
           <t>태성금속</t>
         </is>
       </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L198" s="4" t="n">
+        <v>46066.69375</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -8123,6 +10705,19 @@
           <t>태성금속</t>
         </is>
       </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L199" s="4" t="n">
+        <v>46066.69375</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -8162,6 +10757,19 @@
           <t>청솔전자</t>
         </is>
       </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L200" s="4" t="n">
+        <v>46066.38611111111</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -8201,6 +10809,19 @@
           <t>청솔전자</t>
         </is>
       </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L201" s="4" t="n">
+        <v>46066.38611111111</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -8240,6 +10861,19 @@
           <t>청솔전자</t>
         </is>
       </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L202" s="4" t="n">
+        <v>46066.38611111111</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -8279,6 +10913,19 @@
           <t>우진기공</t>
         </is>
       </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L203" s="4" t="n">
+        <v>46066.41180555556</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -8318,6 +10965,19 @@
           <t>우진기공</t>
         </is>
       </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L204" s="4" t="n">
+        <v>46066.41180555556</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -8357,6 +11017,19 @@
           <t>우진기공</t>
         </is>
       </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L205" s="4" t="n">
+        <v>46066.41180555556</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -8396,6 +11069,19 @@
           <t>보람산업</t>
         </is>
       </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L206" s="4" t="n">
+        <v>46066.4375</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -8435,6 +11121,19 @@
           <t>보람산업</t>
         </is>
       </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L207" s="4" t="n">
+        <v>46066.4375</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -8474,6 +11173,19 @@
           <t>보람산업</t>
         </is>
       </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L208" s="4" t="n">
+        <v>46066.4375</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -8513,6 +11225,19 @@
           <t>다온테크</t>
         </is>
       </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L209" s="4" t="n">
+        <v>46066.46319444444</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -8552,6 +11277,19 @@
           <t>다온테크</t>
         </is>
       </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L210" s="4" t="n">
+        <v>46066.46319444444</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -8591,6 +11329,19 @@
           <t>다온테크</t>
         </is>
       </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L211" s="4" t="n">
+        <v>46066.46319444444</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -8630,6 +11381,19 @@
           <t>해솔정밀</t>
         </is>
       </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L212" s="4" t="n">
+        <v>46066.48888888889</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -8669,6 +11433,19 @@
           <t>해솔정밀</t>
         </is>
       </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L213" s="4" t="n">
+        <v>46066.48888888889</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -8708,6 +11485,19 @@
           <t>해솔정밀</t>
         </is>
       </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L214" s="4" t="n">
+        <v>46066.48888888889</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -8747,6 +11537,19 @@
           <t>새롬전자</t>
         </is>
       </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L215" s="4" t="n">
+        <v>46066.51458333333</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -8786,6 +11589,19 @@
           <t>새롬전자</t>
         </is>
       </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L216" s="4" t="n">
+        <v>46066.51458333333</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -8825,6 +11641,19 @@
           <t>새롬전자</t>
         </is>
       </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L217" s="4" t="n">
+        <v>46066.51458333333</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -8864,6 +11693,19 @@
           <t>은하산업</t>
         </is>
       </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L218" s="4" t="n">
+        <v>46066.54027777778</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -8903,6 +11745,19 @@
           <t>은하산업</t>
         </is>
       </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L219" s="4" t="n">
+        <v>46066.54027777778</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -8942,6 +11797,19 @@
           <t>은하산업</t>
         </is>
       </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L220" s="4" t="n">
+        <v>46066.54027777778</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -8981,6 +11849,19 @@
           <t>이든테크</t>
         </is>
       </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L221" s="4" t="n">
+        <v>46066.56597222222</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -9020,6 +11901,19 @@
           <t>이든테크</t>
         </is>
       </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L222" s="4" t="n">
+        <v>46066.56597222222</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -9059,6 +11953,19 @@
           <t>이든테크</t>
         </is>
       </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L223" s="4" t="n">
+        <v>46066.56597222222</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -9098,6 +12005,19 @@
           <t>한결기계</t>
         </is>
       </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L224" s="4" t="n">
+        <v>46066.59166666667</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -9137,6 +12057,19 @@
           <t>한결기계</t>
         </is>
       </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L225" s="4" t="n">
+        <v>46066.59166666667</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -9176,6 +12109,19 @@
           <t>한결기계</t>
         </is>
       </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L226" s="4" t="n">
+        <v>46066.59166666667</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -9215,6 +12161,19 @@
           <t>지온오토</t>
         </is>
       </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L227" s="4" t="n">
+        <v>46066.61736111111</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -9254,6 +12213,19 @@
           <t>지온오토</t>
         </is>
       </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L228" s="4" t="n">
+        <v>46066.61736111111</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -9293,6 +12265,19 @@
           <t>지온오토</t>
         </is>
       </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L229" s="4" t="n">
+        <v>46066.61736111111</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -9332,6 +12317,19 @@
           <t>유성정밀</t>
         </is>
       </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L230" s="4" t="n">
+        <v>46066.64305555556</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -9371,6 +12369,19 @@
           <t>유성정밀</t>
         </is>
       </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L231" s="4" t="n">
+        <v>46066.64305555556</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -9410,6 +12421,19 @@
           <t>유성정밀</t>
         </is>
       </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L232" s="4" t="n">
+        <v>46066.64305555556</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -9449,6 +12473,19 @@
           <t>라온전자</t>
         </is>
       </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L233" s="4" t="n">
+        <v>46066.66875</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -9488,6 +12525,19 @@
           <t>라온전자</t>
         </is>
       </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L234" s="4" t="n">
+        <v>46066.66875</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -9527,6 +12577,19 @@
           <t>라온전자</t>
         </is>
       </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L235" s="4" t="n">
+        <v>46066.66875</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -9566,6 +12629,19 @@
           <t>나래산업</t>
         </is>
       </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L236" s="4" t="n">
+        <v>46066.69444444445</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -9605,6 +12681,19 @@
           <t>나래산업</t>
         </is>
       </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L237" s="4" t="n">
+        <v>46066.69444444445</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -9644,6 +12733,19 @@
           <t>나래산업</t>
         </is>
       </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L238" s="4" t="n">
+        <v>46066.69444444445</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -9683,6 +12785,19 @@
           <t>누리전자</t>
         </is>
       </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L239" s="4" t="n">
+        <v>46078.38680555556</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -9722,6 +12837,19 @@
           <t>누리전자</t>
         </is>
       </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L240" s="4" t="n">
+        <v>46078.38680555556</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -9761,6 +12889,19 @@
           <t>대영정밀</t>
         </is>
       </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L241" s="4" t="n">
+        <v>46078.4125</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -9800,6 +12941,19 @@
           <t>대영정밀</t>
         </is>
       </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L242" s="4" t="n">
+        <v>46078.4125</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -9839,6 +12993,19 @@
           <t>세진산업</t>
         </is>
       </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L243" s="4" t="n">
+        <v>46078.43819444445</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -9878,6 +13045,19 @@
           <t>세진산업</t>
         </is>
       </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L244" s="4" t="n">
+        <v>46078.43819444445</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -9917,6 +13097,19 @@
           <t>동원테크</t>
         </is>
       </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L245" s="4" t="n">
+        <v>46078.46388888889</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -9956,6 +13149,19 @@
           <t>동원테크</t>
         </is>
       </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L246" s="4" t="n">
+        <v>46078.46388888889</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -9995,6 +13201,19 @@
           <t>미래기계</t>
         </is>
       </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L247" s="4" t="n">
+        <v>46078.48958333334</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -10034,6 +13253,19 @@
           <t>미래기계</t>
         </is>
       </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L248" s="4" t="n">
+        <v>46078.48958333334</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -10073,6 +13305,19 @@
           <t>한빛오토</t>
         </is>
       </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L249" s="4" t="n">
+        <v>46078.51527777778</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -10112,6 +13357,19 @@
           <t>한빛오토</t>
         </is>
       </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L250" s="4" t="n">
+        <v>46078.51527777778</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -10151,6 +13409,19 @@
           <t>태성금속</t>
         </is>
       </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L251" s="4" t="n">
+        <v>46078.54097222222</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -10190,6 +13461,19 @@
           <t>태성금속</t>
         </is>
       </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L252" s="4" t="n">
+        <v>46078.54097222222</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -10229,6 +13513,19 @@
           <t>청솔전자</t>
         </is>
       </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L253" s="4" t="n">
+        <v>46078.56666666667</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -10268,6 +13565,19 @@
           <t>청솔전자</t>
         </is>
       </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L254" s="4" t="n">
+        <v>46078.56666666667</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -10307,6 +13617,19 @@
           <t>우진기공</t>
         </is>
       </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L255" s="4" t="n">
+        <v>46078.59236111111</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -10346,6 +13669,19 @@
           <t>우진기공</t>
         </is>
       </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L256" s="4" t="n">
+        <v>46078.59236111111</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -10385,6 +13721,19 @@
           <t>보람산업</t>
         </is>
       </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L257" s="4" t="n">
+        <v>46078.61805555555</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -10424,6 +13773,19 @@
           <t>보람산업</t>
         </is>
       </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L258" s="4" t="n">
+        <v>46078.61805555555</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -10463,6 +13825,19 @@
           <t>다온테크</t>
         </is>
       </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L259" s="4" t="n">
+        <v>46078.64375</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -10502,6 +13877,19 @@
           <t>다온테크</t>
         </is>
       </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L260" s="4" t="n">
+        <v>46078.64375</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -10541,6 +13929,19 @@
           <t>해솔정밀</t>
         </is>
       </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L261" s="4" t="n">
+        <v>46078.66944444444</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -10580,6 +13981,19 @@
           <t>해솔정밀</t>
         </is>
       </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L262" s="4" t="n">
+        <v>46078.66944444444</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -10619,6 +14033,19 @@
           <t>새롬전자</t>
         </is>
       </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L263" s="4" t="n">
+        <v>46078.69513888889</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -10658,6 +14085,19 @@
           <t>새롬전자</t>
         </is>
       </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L264" s="4" t="n">
+        <v>46078.69513888889</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -10697,6 +14137,19 @@
           <t>은하산업</t>
         </is>
       </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L265" s="4" t="n">
+        <v>46078.3875</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -10736,6 +14189,19 @@
           <t>은하산업</t>
         </is>
       </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L266" s="4" t="n">
+        <v>46078.3875</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -10775,6 +14241,19 @@
           <t>이든테크</t>
         </is>
       </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L267" s="4" t="n">
+        <v>46078.41319444445</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -10814,6 +14293,19 @@
           <t>이든테크</t>
         </is>
       </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L268" s="4" t="n">
+        <v>46078.41319444445</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -10853,6 +14345,19 @@
           <t>한결기계</t>
         </is>
       </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L269" s="4" t="n">
+        <v>46078.43888888889</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -10892,6 +14397,19 @@
           <t>한결기계</t>
         </is>
       </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L270" s="4" t="n">
+        <v>46078.43888888889</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -10931,6 +14449,19 @@
           <t>지온오토</t>
         </is>
       </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L271" s="4" t="n">
+        <v>46078.46458333333</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -10970,6 +14501,19 @@
           <t>지온오토</t>
         </is>
       </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L272" s="4" t="n">
+        <v>46078.46458333333</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -11009,6 +14553,19 @@
           <t>유성정밀</t>
         </is>
       </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L273" s="4" t="n">
+        <v>46078.49027777778</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -11048,6 +14605,19 @@
           <t>유성정밀</t>
         </is>
       </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L274" s="4" t="n">
+        <v>46078.49027777778</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -11087,6 +14657,19 @@
           <t>라온전자</t>
         </is>
       </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L275" s="4" t="n">
+        <v>46078.51597222222</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -11126,6 +14709,19 @@
           <t>라온전자</t>
         </is>
       </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L276" s="4" t="n">
+        <v>46078.51597222222</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -11165,6 +14761,19 @@
           <t>나래산업</t>
         </is>
       </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L277" s="4" t="n">
+        <v>46078.54166666666</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -11204,6 +14813,19 @@
           <t>나래산업</t>
         </is>
       </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L278" s="4" t="n">
+        <v>46078.54166666666</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -11238,6 +14860,19 @@
           <t>2월 급여</t>
         </is>
       </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L279" s="4" t="n">
+        <v>46078.56736111111</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -11272,6 +14907,19 @@
           <t>2월 급여 예수금</t>
         </is>
       </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L280" s="4" t="n">
+        <v>46078.56736111111</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -11306,6 +14954,19 @@
           <t>2월 급여 지급</t>
         </is>
       </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L281" s="4" t="n">
+        <v>46078.56736111111</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -11340,6 +15001,19 @@
           <t>퇴직연금 납부(확정기여형)</t>
         </is>
       </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L282" s="4" t="n">
+        <v>46078.59305555555</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -11374,6 +15048,19 @@
           <t>퇴직연금 납부(확정기여형)</t>
         </is>
       </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>박정훈</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L283" s="4" t="n">
+        <v>46078.59305555555</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -11413,6 +15100,19 @@
           <t>대한소재</t>
         </is>
       </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L284" s="4" t="n">
+        <v>46080.61875</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -11452,6 +15152,19 @@
           <t>대한소재</t>
         </is>
       </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L285" s="4" t="n">
+        <v>46080.61875</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -11491,6 +15204,19 @@
           <t>정우금속</t>
         </is>
       </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L286" s="4" t="n">
+        <v>46080.64444444444</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -11530,6 +15256,19 @@
           <t>정우금속</t>
         </is>
       </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L287" s="4" t="n">
+        <v>46080.64444444444</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -11569,6 +15308,19 @@
           <t>한성부품</t>
         </is>
       </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L288" s="4" t="n">
+        <v>46080.67013888889</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -11608,6 +15360,19 @@
           <t>한성부품</t>
         </is>
       </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L289" s="4" t="n">
+        <v>46080.67013888889</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -11647,6 +15412,19 @@
           <t>동진케미칼</t>
         </is>
       </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L290" s="4" t="n">
+        <v>46080.69583333333</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -11686,6 +15464,19 @@
           <t>동진케미칼</t>
         </is>
       </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L291" s="4" t="n">
+        <v>46080.69583333333</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -11725,6 +15516,19 @@
           <t>서림물산</t>
         </is>
       </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L292" s="4" t="n">
+        <v>46080.38819444444</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -11764,6 +15568,19 @@
           <t>서림물산</t>
         </is>
       </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L293" s="4" t="n">
+        <v>46080.38819444444</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -11803,6 +15620,19 @@
           <t>늘푸른산업</t>
         </is>
       </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L294" s="4" t="n">
+        <v>46080.41388888889</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -11842,6 +15672,19 @@
           <t>늘푸른산업</t>
         </is>
       </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L295" s="4" t="n">
+        <v>46080.41388888889</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -11876,6 +15719,19 @@
           <t>매출원가 대체</t>
         </is>
       </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L296" s="4" t="n">
+        <v>46084.43958333333</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -11910,6 +15766,19 @@
           <t>매출원가 대체</t>
         </is>
       </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L297" s="4" t="n">
+        <v>46084.43958333333</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -11949,6 +15818,19 @@
           <t>가나은행</t>
         </is>
       </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L298" s="4" t="n">
+        <v>46084.46527777778</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -11988,6 +15870,19 @@
           <t>가나은행</t>
         </is>
       </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L299" s="4" t="n">
+        <v>46084.46527777778</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -12027,6 +15922,19 @@
           <t>가나은행</t>
         </is>
       </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L300" s="4" t="n">
+        <v>46084.49097222222</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -12066,6 +15974,19 @@
           <t>가나은행</t>
         </is>
       </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L301" s="4" t="n">
+        <v>46084.49097222222</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -12100,6 +16021,19 @@
           <t>기계장치 감가상각</t>
         </is>
       </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L302" s="4" t="n">
+        <v>46084.51666666667</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -12133,6 +16067,19 @@
         <is>
           <t>기계장치 감가상각</t>
         </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>이수진</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>정태호</t>
+        </is>
+      </c>
+      <c r="L303" s="4" t="n">
+        <v>46084.51666666667</v>
       </c>
     </row>
   </sheetData>
